--- a/sources/table_normalization/xlsx/economy-table104.xlsx
+++ b/sources/table_normalization/xlsx/economy-table104.xlsx
@@ -89,10 +89,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="4">
-    <numFmt numFmtId="167" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="168" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="169" formatCode="0.0"/>
-    <numFmt numFmtId="170" formatCode="#,##0.0"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -325,7 +325,7 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="55">
@@ -334,19 +334,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -355,24 +355,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -392,53 +392,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -466,38 +450,33 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Процентный" xfId="2" builtinId="5"/>
     <cellStyle name="Финансовый" xfId="1" builtinId="3"/>
   </cellStyles>
-  <dxfs count="21">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-0.14993743705557422"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-0.14993743705557422"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-0.14993743705557422"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="18">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -698,25 +677,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
-      <tableStyleElement type="wholeTable" dxfId="20"/>
-      <tableStyleElement type="headerRow" dxfId="19"/>
-      <tableStyleElement type="totalRow" dxfId="18"/>
-      <tableStyleElement type="firstColumn" dxfId="17"/>
-      <tableStyleElement type="lastColumn" dxfId="16"/>
-      <tableStyleElement type="firstRowStripe" dxfId="15"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
+      <tableStyleElement type="wholeTable" dxfId="17"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstColumn" dxfId="14"/>
+      <tableStyleElement type="lastColumn" dxfId="13"/>
+      <tableStyleElement type="firstRowStripe" dxfId="12"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="11"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
-      <tableStyleElement type="headerRow" dxfId="13"/>
-      <tableStyleElement type="totalRow" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="9"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="7"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="6"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="5"/>
-      <tableStyleElement type="pageFieldValues" dxfId="4"/>
+      <tableStyleElement type="headerRow" dxfId="10"/>
+      <tableStyleElement type="totalRow" dxfId="9"/>
+      <tableStyleElement type="firstRowStripe" dxfId="8"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="7"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="6"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="5"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="4"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="3"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="2"/>
+      <tableStyleElement type="pageFieldValues" dxfId="1"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -990,33 +969,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" s="36"/>
-      <c r="B1" s="44" t="s">
+      <c r="A1" s="47"/>
+      <c r="B1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="45"/>
-      <c r="O1" s="45"/>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
-      <c r="T1" s="45"/>
-      <c r="U1" s="45"/>
-      <c r="V1" s="46"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="40"/>
     </row>
     <row r="2" spans="1:22">
-      <c r="A2" s="37"/>
+      <c r="A2" s="48"/>
       <c r="B2" s="1">
         <v>1997</v>
       </c>
@@ -1674,30 +1653,30 @@
       <c r="V12" s="16"/>
     </row>
     <row r="13" spans="1:22">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="53"/>
-      <c r="J13" s="54"/>
-      <c r="K13" s="54"/>
-      <c r="L13" s="54"/>
-      <c r="M13" s="54"/>
-      <c r="N13" s="54"/>
-      <c r="O13" s="54"/>
-      <c r="P13" s="54"/>
-      <c r="Q13" s="54"/>
-      <c r="R13" s="54"/>
-      <c r="S13" s="54"/>
-      <c r="T13" s="54"/>
-      <c r="U13" s="54"/>
-      <c r="V13" s="54"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="37"/>
+      <c r="K13" s="37"/>
+      <c r="L13" s="37"/>
+      <c r="M13" s="37"/>
+      <c r="N13" s="37"/>
+      <c r="O13" s="37"/>
+      <c r="P13" s="37"/>
+      <c r="Q13" s="37"/>
+      <c r="R13" s="37"/>
+      <c r="S13" s="37"/>
+      <c r="T13" s="37"/>
+      <c r="U13" s="37"/>
+      <c r="V13" s="37"/>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="8" t="s">
@@ -1836,30 +1815,30 @@
       </c>
     </row>
     <row r="16" spans="1:22">
-      <c r="A16" s="47" t="s">
+      <c r="A16" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="48"/>
-      <c r="H16" s="48"/>
-      <c r="I16" s="48"/>
-      <c r="J16" s="48"/>
-      <c r="K16" s="48"/>
-      <c r="L16" s="48"/>
-      <c r="M16" s="48"/>
-      <c r="N16" s="48"/>
-      <c r="O16" s="48"/>
-      <c r="P16" s="48"/>
-      <c r="Q16" s="48"/>
-      <c r="R16" s="48"/>
-      <c r="S16" s="48"/>
-      <c r="T16" s="48"/>
-      <c r="U16" s="48"/>
-      <c r="V16" s="49"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="42"/>
+      <c r="L16" s="42"/>
+      <c r="M16" s="42"/>
+      <c r="N16" s="42"/>
+      <c r="O16" s="42"/>
+      <c r="P16" s="42"/>
+      <c r="Q16" s="42"/>
+      <c r="R16" s="42"/>
+      <c r="S16" s="42"/>
+      <c r="T16" s="42"/>
+      <c r="U16" s="42"/>
+      <c r="V16" s="43"/>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="2" t="s">
@@ -2454,30 +2433,30 @@
       <c r="V26" s="16"/>
     </row>
     <row r="27" spans="1:22">
-      <c r="A27" s="53" t="s">
+      <c r="A27" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="B27" s="54"/>
-      <c r="C27" s="53"/>
-      <c r="D27" s="53"/>
-      <c r="E27" s="53"/>
-      <c r="F27" s="53"/>
-      <c r="G27" s="53"/>
-      <c r="H27" s="53"/>
-      <c r="I27" s="53"/>
-      <c r="J27" s="54"/>
-      <c r="K27" s="54"/>
-      <c r="L27" s="54"/>
-      <c r="M27" s="54"/>
-      <c r="N27" s="54"/>
-      <c r="O27" s="54"/>
-      <c r="P27" s="54"/>
-      <c r="Q27" s="54"/>
-      <c r="R27" s="54"/>
-      <c r="S27" s="54"/>
-      <c r="T27" s="54"/>
-      <c r="U27" s="54"/>
-      <c r="V27" s="54"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="36"/>
+      <c r="G27" s="36"/>
+      <c r="H27" s="36"/>
+      <c r="I27" s="36"/>
+      <c r="J27" s="37"/>
+      <c r="K27" s="37"/>
+      <c r="L27" s="37"/>
+      <c r="M27" s="37"/>
+      <c r="N27" s="37"/>
+      <c r="O27" s="37"/>
+      <c r="P27" s="37"/>
+      <c r="Q27" s="37"/>
+      <c r="R27" s="37"/>
+      <c r="S27" s="37"/>
+      <c r="T27" s="37"/>
+      <c r="U27" s="37"/>
+      <c r="V27" s="37"/>
     </row>
     <row r="28" spans="1:22">
       <c r="A28" s="8" t="s">
@@ -2616,30 +2595,30 @@
       </c>
     </row>
     <row r="30" spans="1:22">
-      <c r="A30" s="50" t="s">
+      <c r="A30" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="B30" s="51"/>
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="51"/>
-      <c r="F30" s="51"/>
-      <c r="G30" s="51"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="51"/>
-      <c r="J30" s="51"/>
-      <c r="K30" s="51"/>
-      <c r="L30" s="51"/>
-      <c r="M30" s="51"/>
-      <c r="N30" s="51"/>
-      <c r="O30" s="51"/>
-      <c r="P30" s="51"/>
-      <c r="Q30" s="51"/>
-      <c r="R30" s="51"/>
-      <c r="S30" s="51"/>
-      <c r="T30" s="51"/>
-      <c r="U30" s="51"/>
-      <c r="V30" s="52"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="45"/>
+      <c r="D30" s="45"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="45"/>
+      <c r="H30" s="45"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="45"/>
+      <c r="K30" s="45"/>
+      <c r="L30" s="45"/>
+      <c r="M30" s="45"/>
+      <c r="N30" s="45"/>
+      <c r="O30" s="45"/>
+      <c r="P30" s="45"/>
+      <c r="Q30" s="45"/>
+      <c r="R30" s="45"/>
+      <c r="S30" s="45"/>
+      <c r="T30" s="45"/>
+      <c r="U30" s="45"/>
+      <c r="V30" s="46"/>
     </row>
     <row r="31" spans="1:22">
       <c r="A31" s="2" t="s">
@@ -3234,30 +3213,30 @@
       <c r="V40" s="26"/>
     </row>
     <row r="41" spans="1:22">
-      <c r="A41" s="53" t="s">
+      <c r="A41" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="B41" s="54"/>
-      <c r="C41" s="53"/>
-      <c r="D41" s="53"/>
-      <c r="E41" s="53"/>
-      <c r="F41" s="53"/>
-      <c r="G41" s="53"/>
-      <c r="H41" s="53"/>
-      <c r="I41" s="53"/>
-      <c r="J41" s="54"/>
-      <c r="K41" s="54"/>
-      <c r="L41" s="54"/>
-      <c r="M41" s="54"/>
-      <c r="N41" s="54"/>
-      <c r="O41" s="54"/>
-      <c r="P41" s="54"/>
-      <c r="Q41" s="54"/>
-      <c r="R41" s="54"/>
-      <c r="S41" s="54"/>
-      <c r="T41" s="54"/>
-      <c r="U41" s="54"/>
-      <c r="V41" s="54"/>
+      <c r="B41" s="37"/>
+      <c r="C41" s="36"/>
+      <c r="D41" s="36"/>
+      <c r="E41" s="36"/>
+      <c r="F41" s="36"/>
+      <c r="G41" s="36"/>
+      <c r="H41" s="36"/>
+      <c r="I41" s="36"/>
+      <c r="J41" s="37"/>
+      <c r="K41" s="37"/>
+      <c r="L41" s="37"/>
+      <c r="M41" s="37"/>
+      <c r="N41" s="37"/>
+      <c r="O41" s="37"/>
+      <c r="P41" s="37"/>
+      <c r="Q41" s="37"/>
+      <c r="R41" s="37"/>
+      <c r="S41" s="37"/>
+      <c r="T41" s="37"/>
+      <c r="U41" s="37"/>
+      <c r="V41" s="37"/>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" s="8" t="s">
@@ -3396,54 +3375,54 @@
       </c>
     </row>
     <row r="44" spans="1:22" ht="27" customHeight="1">
-      <c r="A44" s="38" t="s">
+      <c r="A44" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="B44" s="39"/>
-      <c r="C44" s="39"/>
-      <c r="D44" s="39"/>
-      <c r="E44" s="39"/>
-      <c r="F44" s="39"/>
-      <c r="G44" s="39"/>
-      <c r="H44" s="39"/>
-      <c r="I44" s="39"/>
-      <c r="J44" s="39"/>
-      <c r="K44" s="39"/>
-      <c r="L44" s="39"/>
-      <c r="M44" s="39"/>
-      <c r="N44" s="39"/>
-      <c r="O44" s="39"/>
-      <c r="P44" s="39"/>
-      <c r="Q44" s="39"/>
-      <c r="R44" s="39"/>
-      <c r="S44" s="39"/>
-      <c r="T44" s="39"/>
-      <c r="U44" s="39"/>
-      <c r="V44" s="40"/>
+      <c r="B44" s="50"/>
+      <c r="C44" s="50"/>
+      <c r="D44" s="50"/>
+      <c r="E44" s="50"/>
+      <c r="F44" s="50"/>
+      <c r="G44" s="50"/>
+      <c r="H44" s="50"/>
+      <c r="I44" s="50"/>
+      <c r="J44" s="50"/>
+      <c r="K44" s="50"/>
+      <c r="L44" s="50"/>
+      <c r="M44" s="50"/>
+      <c r="N44" s="50"/>
+      <c r="O44" s="50"/>
+      <c r="P44" s="50"/>
+      <c r="Q44" s="50"/>
+      <c r="R44" s="50"/>
+      <c r="S44" s="50"/>
+      <c r="T44" s="50"/>
+      <c r="U44" s="50"/>
+      <c r="V44" s="51"/>
     </row>
     <row r="45" spans="1:22">
-      <c r="A45" s="41"/>
-      <c r="B45" s="42"/>
-      <c r="C45" s="42"/>
-      <c r="D45" s="42"/>
-      <c r="E45" s="42"/>
-      <c r="F45" s="42"/>
-      <c r="G45" s="42"/>
-      <c r="H45" s="42"/>
-      <c r="I45" s="42"/>
-      <c r="J45" s="42"/>
-      <c r="K45" s="42"/>
-      <c r="L45" s="42"/>
-      <c r="M45" s="42"/>
-      <c r="N45" s="42"/>
-      <c r="O45" s="42"/>
-      <c r="P45" s="42"/>
-      <c r="Q45" s="42"/>
-      <c r="R45" s="42"/>
-      <c r="S45" s="42"/>
-      <c r="T45" s="42"/>
-      <c r="U45" s="42"/>
-      <c r="V45" s="43"/>
+      <c r="A45" s="52"/>
+      <c r="B45" s="53"/>
+      <c r="C45" s="53"/>
+      <c r="D45" s="53"/>
+      <c r="E45" s="53"/>
+      <c r="F45" s="53"/>
+      <c r="G45" s="53"/>
+      <c r="H45" s="53"/>
+      <c r="I45" s="53"/>
+      <c r="J45" s="53"/>
+      <c r="K45" s="53"/>
+      <c r="L45" s="53"/>
+      <c r="M45" s="53"/>
+      <c r="N45" s="53"/>
+      <c r="O45" s="53"/>
+      <c r="P45" s="53"/>
+      <c r="Q45" s="53"/>
+      <c r="R45" s="53"/>
+      <c r="S45" s="53"/>
+      <c r="T45" s="53"/>
+      <c r="U45" s="53"/>
+      <c r="V45" s="54"/>
     </row>
     <row r="46" spans="1:22" hidden="1">
       <c r="A46" s="22"/>
@@ -5586,7 +5565,7 @@
     <mergeCell ref="A44:V45"/>
   </mergeCells>
   <conditionalFormatting sqref="A31:V40 A16 A3:V12 A17:V26 A30 A14:V15 A42:V43 A28:V29">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD(ROW(),2)=1</formula>
     </cfRule>
   </conditionalFormatting>
